--- a/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0261</v>
+        <v>0.0233</v>
       </c>
       <c r="E2">
-        <v>0.017365</v>
+        <v>-0.00927</v>
       </c>
       <c r="F2">
-        <v>0.25</v>
+        <v>0.026</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001558415159539929</v>
+        <v>-0.0001946323066527286</v>
       </c>
       <c r="J2">
-        <v>-0.000133115227629712</v>
+        <v>-0.0001673071497335933</v>
       </c>
       <c r="K2">
-        <v>6132</v>
+        <v>6721.6</v>
       </c>
       <c r="L2">
-        <v>0.3462391941412624</v>
+        <v>0.3882019324620121</v>
       </c>
       <c r="M2">
-        <v>851.6392000000001</v>
+        <v>6098.400000000001</v>
       </c>
       <c r="N2">
-        <v>0.01500252261901406</v>
+        <v>0.1255812229466202</v>
       </c>
       <c r="O2">
-        <v>0.1388844096542727</v>
+        <v>0.9072839800047608</v>
       </c>
       <c r="P2">
-        <v>851.6392000000001</v>
+        <v>6093.900000000001</v>
       </c>
       <c r="Q2">
-        <v>0.01500252261901406</v>
+        <v>0.1254885567549535</v>
       </c>
       <c r="R2">
-        <v>0.1388844096542727</v>
+        <v>0.9066144965484408</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0007378984651711923</v>
       </c>
       <c r="U2">
-        <v>149764.1</v>
+        <v>123538.1</v>
       </c>
       <c r="V2">
-        <v>2.638252557851123</v>
+        <v>2.543956722829243</v>
       </c>
       <c r="W2">
-        <v>0.117635065427573</v>
+        <v>0.1076761732357627</v>
       </c>
       <c r="X2">
-        <v>0.06456324736901989</v>
+        <v>0.1049746304502861</v>
       </c>
       <c r="Y2">
-        <v>0.05307181805855309</v>
+        <v>0.00270154278547656</v>
       </c>
       <c r="Z2">
-        <v>0.1482069439342043</v>
+        <v>0.3068165306361127</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04314929676573571</v>
+        <v>0.0692276667199095</v>
       </c>
       <c r="AC2">
-        <v>-0.04314929676573571</v>
+        <v>-0.0697543742048829</v>
       </c>
       <c r="AD2">
-        <v>145659.5</v>
+        <v>133131</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>145659.5</v>
+        <v>133131</v>
       </c>
       <c r="AG2">
-        <v>-4104.600000000006</v>
+        <v>9592.899999999994</v>
       </c>
       <c r="AH2">
-        <v>0.7195694819684636</v>
+        <v>0.7327274008158845</v>
       </c>
       <c r="AI2">
-        <v>0.683504061340078</v>
+        <v>0.7088464307164124</v>
       </c>
       <c r="AJ2">
-        <v>-0.07794264533304988</v>
+        <v>0.164955987777344</v>
       </c>
       <c r="AK2">
-        <v>-0.06479968552118716</v>
+        <v>0.149246602515733</v>
       </c>
       <c r="AL2">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="AM2">
-        <v>-24</v>
+        <v>-844.8</v>
       </c>
       <c r="AO2">
-        <v>-0.1682926829268293</v>
+        <v>-0.2373239436619718</v>
       </c>
       <c r="AQ2">
-        <v>0.115</v>
+        <v>0.003989109848484849</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KBC Ancora SCA (ENXTBR:KBCA)</t>
+          <t>BNP Paribas Fortis SA (ENXTBR:017250539)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,26 +718,47 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.033</v>
+      </c>
+      <c r="E3">
+        <v>0.119</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
-        <v>628</v>
+        <v>3223.9</v>
+      </c>
+      <c r="L3">
+        <v>0.3492206202541244</v>
       </c>
       <c r="M3">
-        <v>18.6</v>
+        <v>993.1</v>
       </c>
       <c r="N3">
-        <v>0.004968479538412224</v>
+        <v>0.05425619676680925</v>
       </c>
       <c r="O3">
-        <v>0.02961783439490446</v>
+        <v>0.3080430534445858</v>
       </c>
       <c r="P3">
-        <v>18.6</v>
+        <v>993.1</v>
       </c>
       <c r="Q3">
-        <v>0.004968479538412224</v>
+        <v>0.05425619676680925</v>
       </c>
       <c r="R3">
-        <v>0.02961783439490446</v>
+        <v>0.3080430534445858</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,67 +767,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>76.3</v>
+        <v>70825.8</v>
       </c>
       <c r="V3">
-        <v>0.02038145100972326</v>
+        <v>3.869437660826381</v>
       </c>
       <c r="W3">
-        <v>0.1988915281076801</v>
+        <v>0.1076761732357627</v>
       </c>
       <c r="X3">
-        <v>0.04448596015004314</v>
+        <v>0.1855738916910704</v>
       </c>
       <c r="Y3">
-        <v>0.154405567957637</v>
+        <v>-0.07789771845530767</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.1817295975716105</v>
       </c>
       <c r="AA3">
-        <v>-0.0007945418429916227</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04222045042316872</v>
+        <v>0.06737246849582462</v>
       </c>
       <c r="AC3">
-        <v>-0.04301499226616035</v>
+        <v>-0.06737246849582462</v>
       </c>
       <c r="AD3">
-        <v>406.7</v>
+        <v>91882.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>406.7</v>
+        <v>91882.7</v>
       </c>
       <c r="AG3">
-        <v>330.4</v>
+        <v>21056.89999999999</v>
       </c>
       <c r="AH3">
-        <v>0.09799291617473435</v>
+        <v>0.8338827044304842</v>
       </c>
       <c r="AI3">
-        <v>0.09364710216675494</v>
+        <v>0.74506212182397</v>
       </c>
       <c r="AJ3">
-        <v>0.08109965635738831</v>
+        <v>0.5349713420458933</v>
       </c>
       <c r="AK3">
-        <v>0.07743870997984344</v>
+        <v>0.4011113142996471</v>
       </c>
       <c r="AL3">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-24</v>
-      </c>
-      <c r="AO3">
-        <v>-0.1682926829268293</v>
-      </c>
-      <c r="AQ3">
-        <v>0.115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -817,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNP Paribas Fortis SA (ENXTBR:017250539)</t>
+          <t>KBC Group NV (ENXTBR:KBC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,10 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.022</v>
+        <v>0.0136</v>
       </c>
       <c r="E4">
-        <v>0.0438</v>
+        <v>-0.0109</v>
+      </c>
+      <c r="F4">
+        <v>0.026</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,28 +862,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2619.2</v>
+        <v>2656.4</v>
       </c>
       <c r="L4">
-        <v>0.2981140236060051</v>
+        <v>0.3286403563033528</v>
       </c>
       <c r="M4">
-        <v>562.9392</v>
+        <v>4381.3</v>
       </c>
       <c r="N4">
-        <v>0.03260637022363551</v>
+        <v>0.1636339869281046</v>
       </c>
       <c r="O4">
-        <v>0.2149279169211973</v>
+        <v>1.64933744917934</v>
       </c>
       <c r="P4">
-        <v>562.9392</v>
+        <v>4381.3</v>
       </c>
       <c r="Q4">
-        <v>0.03260637022363551</v>
+        <v>0.1636339869281046</v>
       </c>
       <c r="R4">
-        <v>0.2149279169211973</v>
+        <v>1.64933744917934</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,55 +892,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>84413.10000000001</v>
+        <v>52632.9</v>
       </c>
       <c r="V4">
-        <v>4.889346469964726</v>
+        <v>1.965747899159664</v>
       </c>
       <c r="W4">
-        <v>0.09891724291600418</v>
+        <v>0.09713253523083787</v>
       </c>
       <c r="X4">
-        <v>0.1675574573518255</v>
+        <v>0.1049746304502861</v>
       </c>
       <c r="Y4">
-        <v>-0.06864021443582133</v>
+        <v>-0.007842095219448258</v>
       </c>
       <c r="Z4">
-        <v>0.1018586576207049</v>
+        <v>5.909921766469267</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04314929676573571</v>
+        <v>0.0697543742048829</v>
       </c>
       <c r="AC4">
-        <v>-0.04314929676573571</v>
+        <v>-0.0697543742048829</v>
       </c>
       <c r="AD4">
-        <v>106139.4</v>
+        <v>40994.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>106139.4</v>
+        <v>40994.3</v>
       </c>
       <c r="AG4">
-        <v>21726.29999999999</v>
+        <v>-11638.6</v>
       </c>
       <c r="AH4">
-        <v>0.8600962204659327</v>
+        <v>0.604909597708697</v>
       </c>
       <c r="AI4">
-        <v>0.7458716466681892</v>
+        <v>0.6759694089556965</v>
       </c>
       <c r="AJ4">
-        <v>0.5572132030468568</v>
+        <v>-0.7689146692740676</v>
       </c>
       <c r="AK4">
-        <v>0.375307051031795</v>
+        <v>-1.452591640352957</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -939,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KBC Group NV (ENXTBR:KBC)</t>
+          <t>KBC Ancora SCA (ENXTBR:KBCA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,113 +965,98 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0302</v>
-      </c>
       <c r="E5">
-        <v>-0.00907</v>
-      </c>
-      <c r="F5">
-        <v>0.25</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
+        <v>-0.00927</v>
       </c>
       <c r="K5">
-        <v>2884.8</v>
-      </c>
-      <c r="L5">
-        <v>0.3232486217560845</v>
+        <v>841.3</v>
       </c>
       <c r="M5">
-        <v>270.1</v>
+        <v>724</v>
       </c>
       <c r="N5">
-        <v>0.007553533325316502</v>
+        <v>0.2078966259870783</v>
       </c>
       <c r="O5">
-        <v>0.09362867443150305</v>
+        <v>0.8605729228574825</v>
       </c>
       <c r="P5">
-        <v>270.1</v>
+        <v>719.5</v>
       </c>
       <c r="Q5">
-        <v>0.007553533325316502</v>
+        <v>0.2066044508255563</v>
       </c>
       <c r="R5">
-        <v>0.09362867443150305</v>
+        <v>0.8552240580054677</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.006215469613259668</v>
       </c>
       <c r="U5">
-        <v>65274.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V5">
-        <v>1.825452135320389</v>
+        <v>0.02279971284996411</v>
       </c>
       <c r="W5">
-        <v>0.117635065427573</v>
+        <v>0.2137340582287485</v>
       </c>
       <c r="X5">
-        <v>0.06456324736901989</v>
+        <v>0.07128826029935961</v>
       </c>
       <c r="Y5">
-        <v>0.05307181805855309</v>
+        <v>0.1424457979293889</v>
       </c>
       <c r="Z5">
-        <v>0.2998024697993792</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>-0.0007898560915014298</v>
       </c>
       <c r="AB5">
-        <v>0.0438064283123661</v>
+        <v>0.0692276667199095</v>
       </c>
       <c r="AC5">
-        <v>-0.0438064283123661</v>
+        <v>-0.07001752281141092</v>
       </c>
       <c r="AD5">
-        <v>39113.4</v>
+        <v>254</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>39113.4</v>
+        <v>254</v>
       </c>
       <c r="AG5">
-        <v>-26161.3</v>
+        <v>174.6</v>
       </c>
       <c r="AH5">
-        <v>0.522407057425055</v>
+        <v>0.06797805432891743</v>
       </c>
       <c r="AI5">
-        <v>0.5885112606377216</v>
+        <v>0.06603920752950965</v>
       </c>
       <c r="AJ5">
-        <v>-2.726044098032676</v>
+        <v>0.04774274698531623</v>
       </c>
       <c r="AK5">
-        <v>-22.04170528266904</v>
+        <v>0.04635234151003505</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-844.8</v>
+      </c>
+      <c r="AO5">
+        <v>-0.2373239436619718</v>
+      </c>
+      <c r="AQ5">
+        <v>0.003989109848484849</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0233</v>
+        <v>0.04604999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.00927</v>
+        <v>0.0755</v>
       </c>
       <c r="F2">
-        <v>0.026</v>
+        <v>0.0696</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001946323066527286</v>
+        <v>-0.0001601584112285606</v>
       </c>
       <c r="J2">
-        <v>-0.0001673071497335933</v>
+        <v>-0.0001371543059525774</v>
       </c>
       <c r="K2">
-        <v>6721.6</v>
+        <v>7264.1</v>
       </c>
       <c r="L2">
-        <v>0.3882019324620121</v>
+        <v>0.3525474893955719</v>
       </c>
       <c r="M2">
-        <v>6098.400000000001</v>
+        <v>5134.900000000001</v>
       </c>
       <c r="N2">
-        <v>0.1255812229466202</v>
+        <v>0.09140101708974206</v>
       </c>
       <c r="O2">
-        <v>0.9072839800047608</v>
+        <v>0.7068872950537576</v>
       </c>
       <c r="P2">
-        <v>6093.900000000001</v>
+        <v>4924.1</v>
       </c>
       <c r="Q2">
-        <v>0.1254885567549535</v>
+        <v>0.08764878541969637</v>
       </c>
       <c r="R2">
-        <v>0.9066144965484408</v>
+        <v>0.6778678707616911</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>210.8000000000001</v>
       </c>
       <c r="T2">
-        <v>0.0007378984651711923</v>
+        <v>0.04105240608385753</v>
       </c>
       <c r="U2">
-        <v>123538.1</v>
+        <v>106724.915</v>
       </c>
       <c r="V2">
-        <v>2.543956722829243</v>
+        <v>1.899699269667621</v>
       </c>
       <c r="W2">
-        <v>0.1076761732357627</v>
+        <v>0.1309478388837412</v>
       </c>
       <c r="X2">
-        <v>0.1049746304502861</v>
+        <v>0.09012358578028</v>
       </c>
       <c r="Y2">
-        <v>0.00270154278547656</v>
+        <v>0.0408242531034612</v>
       </c>
       <c r="Z2">
-        <v>0.3068165306361127</v>
+        <v>0.3569231089030702</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0692276667199095</v>
+        <v>0.05961262096857506</v>
       </c>
       <c r="AC2">
-        <v>-0.0697543742048829</v>
+        <v>-0.05961262096857506</v>
       </c>
       <c r="AD2">
-        <v>133131</v>
+        <v>170203.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>133131</v>
+        <v>170203.4</v>
       </c>
       <c r="AG2">
-        <v>9592.899999999994</v>
+        <v>63478.485</v>
       </c>
       <c r="AH2">
-        <v>0.7327274008158845</v>
+        <v>0.7518372600805802</v>
       </c>
       <c r="AI2">
-        <v>0.7088464307164124</v>
+        <v>0.7349078123630441</v>
       </c>
       <c r="AJ2">
-        <v>0.164955987777344</v>
+        <v>0.5304975911215917</v>
       </c>
       <c r="AK2">
-        <v>0.149246602515733</v>
+        <v>0.5083427905794337</v>
       </c>
       <c r="AL2">
-        <v>14.2</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AM2">
-        <v>-844.8</v>
+        <v>-329.62</v>
       </c>
       <c r="AO2">
-        <v>-0.2373239436619718</v>
+        <v>-0.3374233128834356</v>
       </c>
       <c r="AQ2">
-        <v>0.003989109848484849</v>
+        <v>0.01001152842667314</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.033</v>
+        <v>0.0488</v>
       </c>
       <c r="E3">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,28 +737,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3223.9</v>
+        <v>3363.5</v>
       </c>
       <c r="L3">
-        <v>0.3492206202541244</v>
+        <v>0.3142253902710176</v>
       </c>
       <c r="M3">
-        <v>993.1</v>
+        <v>2826.4</v>
       </c>
       <c r="N3">
-        <v>0.05425619676680925</v>
+        <v>0.1094998818374471</v>
       </c>
       <c r="O3">
-        <v>0.3080430534445858</v>
+        <v>0.8403151479114018</v>
       </c>
       <c r="P3">
-        <v>993.1</v>
+        <v>2826.4</v>
       </c>
       <c r="Q3">
-        <v>0.05425619676680925</v>
+        <v>0.1094998818374471</v>
       </c>
       <c r="R3">
-        <v>0.3080430534445858</v>
+        <v>0.8403151479114018</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,55 +767,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>70825.8</v>
+        <v>60538.2</v>
       </c>
       <c r="V3">
-        <v>3.869437660826381</v>
+        <v>2.345360085851874</v>
       </c>
       <c r="W3">
-        <v>0.1076761732357627</v>
+        <v>0.1309478388837412</v>
       </c>
       <c r="X3">
-        <v>0.1855738916910704</v>
+        <v>0.135962191864459</v>
       </c>
       <c r="Y3">
-        <v>-0.07789771845530767</v>
+        <v>-0.005014352980717812</v>
       </c>
       <c r="Z3">
-        <v>0.1817295975716105</v>
+        <v>0.232954582550768</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06737246849582462</v>
+        <v>0.0576636278181325</v>
       </c>
       <c r="AC3">
-        <v>-0.06737246849582462</v>
+        <v>-0.0576636278181325</v>
       </c>
       <c r="AD3">
-        <v>91882.7</v>
+        <v>120695.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>91882.7</v>
+        <v>120695.4</v>
       </c>
       <c r="AG3">
-        <v>21056.89999999999</v>
+        <v>60157.2</v>
       </c>
       <c r="AH3">
-        <v>0.8338827044304842</v>
+        <v>0.8238183353320961</v>
       </c>
       <c r="AI3">
-        <v>0.74506212182397</v>
+        <v>0.788695929468162</v>
       </c>
       <c r="AJ3">
-        <v>0.5349713420458933</v>
+        <v>0.6997537487306484</v>
       </c>
       <c r="AK3">
-        <v>0.4011113142996471</v>
+        <v>0.6503945146356389</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0136</v>
+        <v>0.0433</v>
       </c>
       <c r="E4">
-        <v>-0.0109</v>
+        <v>0.0755</v>
       </c>
       <c r="F4">
-        <v>0.026</v>
+        <v>0.0696</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,85 +862,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2656.4</v>
+        <v>3574.3</v>
       </c>
       <c r="L4">
-        <v>0.3286403563033528</v>
+        <v>0.3610221705974446</v>
       </c>
       <c r="M4">
-        <v>4381.3</v>
+        <v>1980.3</v>
       </c>
       <c r="N4">
-        <v>0.1636339869281046</v>
+        <v>0.07379926659113947</v>
       </c>
       <c r="O4">
-        <v>1.64933744917934</v>
+        <v>0.5540385530033853</v>
       </c>
       <c r="P4">
-        <v>4381.3</v>
+        <v>1819.4</v>
       </c>
       <c r="Q4">
-        <v>0.1636339869281046</v>
+        <v>0.0678030528889154</v>
       </c>
       <c r="R4">
-        <v>1.64933744917934</v>
+        <v>0.5090227457124472</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>160.9000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.08125031560874618</v>
       </c>
       <c r="U4">
-        <v>52632.9</v>
+        <v>46186.5</v>
       </c>
       <c r="V4">
-        <v>1.965747899159664</v>
+        <v>1.721218919563532</v>
       </c>
       <c r="W4">
-        <v>0.09713253523083787</v>
+        <v>0.1818898879949519</v>
       </c>
       <c r="X4">
-        <v>0.1049746304502861</v>
+        <v>0.09012358578028</v>
       </c>
       <c r="Y4">
-        <v>-0.007842095219448258</v>
+        <v>0.09176630221467187</v>
       </c>
       <c r="Z4">
-        <v>5.909921766469267</v>
+        <v>1.235662668646955</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0697543742048829</v>
+        <v>0.05961262096857506</v>
       </c>
       <c r="AC4">
-        <v>-0.0697543742048829</v>
+        <v>-0.05961262096857506</v>
       </c>
       <c r="AD4">
-        <v>40994.3</v>
+        <v>49398.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>40994.3</v>
+        <v>49398.8</v>
       </c>
       <c r="AG4">
-        <v>-11638.6</v>
+        <v>3212.300000000003</v>
       </c>
       <c r="AH4">
-        <v>0.604909597708697</v>
+        <v>0.6480026865217415</v>
       </c>
       <c r="AI4">
-        <v>0.6759694089556965</v>
+        <v>0.6616669858997215</v>
       </c>
       <c r="AJ4">
-        <v>-0.7689146692740676</v>
+        <v>0.1069130896395183</v>
       </c>
       <c r="AK4">
-        <v>-1.452591640352957</v>
+        <v>0.1128247095351158</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -966,97 +966,97 @@
         </is>
       </c>
       <c r="E5">
-        <v>-0.00927</v>
+        <v>0.068</v>
       </c>
       <c r="K5">
-        <v>841.3</v>
+        <v>326.3</v>
       </c>
       <c r="M5">
-        <v>724</v>
+        <v>328.2</v>
       </c>
       <c r="N5">
-        <v>0.2078966259870783</v>
+        <v>0.09285875961973743</v>
       </c>
       <c r="O5">
-        <v>0.8605729228574825</v>
+        <v>1.005822862396567</v>
       </c>
       <c r="P5">
-        <v>719.5</v>
+        <v>278.3</v>
       </c>
       <c r="Q5">
-        <v>0.2066044508255563</v>
+        <v>0.07874038026256225</v>
       </c>
       <c r="R5">
-        <v>0.8552240580054677</v>
+        <v>0.8528961078761875</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>49.89999999999998</v>
       </c>
       <c r="T5">
-        <v>0.006215469613259668</v>
+        <v>0.152041438147471</v>
       </c>
       <c r="U5">
-        <v>79.40000000000001</v>
+        <v>0.215</v>
       </c>
       <c r="V5">
-        <v>0.02279971284996411</v>
+        <v>6.083069262109551e-05</v>
       </c>
       <c r="W5">
-        <v>0.2137340582287485</v>
+        <v>0.09083569957129337</v>
       </c>
       <c r="X5">
-        <v>0.07128826029935961</v>
+        <v>0.06085776077857287</v>
       </c>
       <c r="Y5">
-        <v>0.1424457979293889</v>
+        <v>0.0299779387927205</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.0007898560915014298</v>
+        <v>-0.0008760751831793565</v>
       </c>
       <c r="AB5">
-        <v>0.0692276667199095</v>
+        <v>0.06019308409016239</v>
       </c>
       <c r="AC5">
-        <v>-0.07001752281141092</v>
+        <v>-0.06106915927334174</v>
       </c>
       <c r="AD5">
-        <v>254</v>
+        <v>109.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>254</v>
+        <v>109.2</v>
       </c>
       <c r="AG5">
-        <v>174.6</v>
+        <v>108.985</v>
       </c>
       <c r="AH5">
-        <v>0.06797805432891743</v>
+        <v>0.02997035898561862</v>
       </c>
       <c r="AI5">
-        <v>0.06603920752950965</v>
+        <v>0.02793839226321445</v>
       </c>
       <c r="AJ5">
-        <v>0.04774274698531623</v>
+        <v>0.02991311651115652</v>
       </c>
       <c r="AK5">
-        <v>0.04635234151003505</v>
+        <v>0.02788491921855191</v>
       </c>
       <c r="AL5">
-        <v>14.2</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AM5">
-        <v>-844.8</v>
+        <v>-329.62</v>
       </c>
       <c r="AO5">
-        <v>-0.2373239436619718</v>
+        <v>-0.3374233128834356</v>
       </c>
       <c r="AQ5">
-        <v>0.003989109848484849</v>
+        <v>0.01001152842667314</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04604999999999999</v>
+        <v>0.07050000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0755</v>
+        <v>0.05839999999999999</v>
       </c>
       <c r="F2">
-        <v>0.0696</v>
+        <v>0.0426</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001601584112285606</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>-0.0001371543059525774</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>7264.1</v>
+        <v>6447.9</v>
       </c>
       <c r="L2">
-        <v>0.3525474893955719</v>
+        <v>0.2819962213319804</v>
       </c>
       <c r="M2">
-        <v>5134.900000000001</v>
+        <v>7207.4</v>
       </c>
       <c r="N2">
-        <v>0.09140101708974206</v>
+        <v>0.1479211732882363</v>
       </c>
       <c r="O2">
-        <v>0.7068872950537576</v>
+        <v>1.117790288310923</v>
       </c>
       <c r="P2">
-        <v>4924.1</v>
+        <v>5496.5</v>
       </c>
       <c r="Q2">
-        <v>0.08764878541969637</v>
+        <v>0.1128074935453549</v>
       </c>
       <c r="R2">
-        <v>0.6778678707616911</v>
+        <v>0.8524480838722686</v>
       </c>
       <c r="S2">
-        <v>210.8000000000001</v>
+        <v>1710.9</v>
       </c>
       <c r="T2">
-        <v>0.04105240608385753</v>
+        <v>0.2373810250575797</v>
       </c>
       <c r="U2">
-        <v>106724.915</v>
+        <v>71395.60000000001</v>
       </c>
       <c r="V2">
-        <v>1.899699269667621</v>
+        <v>1.465288581127398</v>
       </c>
       <c r="W2">
-        <v>0.1309478388837412</v>
+        <v>0.125314893709658</v>
       </c>
       <c r="X2">
-        <v>0.09012358578028</v>
+        <v>0.1298635266644825</v>
       </c>
       <c r="Y2">
-        <v>0.0408242531034612</v>
+        <v>-0.004548632954824466</v>
       </c>
       <c r="Z2">
-        <v>0.3569231089030702</v>
+        <v>0.200727581738822</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05961262096857506</v>
+        <v>0.06176884452895762</v>
       </c>
       <c r="AC2">
-        <v>-0.05961262096857506</v>
+        <v>-0.06176884452895762</v>
       </c>
       <c r="AD2">
-        <v>170203.4</v>
+        <v>172198.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>170203.4</v>
+        <v>172198.3</v>
       </c>
       <c r="AG2">
-        <v>63478.485</v>
+        <v>100802.7</v>
       </c>
       <c r="AH2">
-        <v>0.7518372600805802</v>
+        <v>0.7794497537376162</v>
       </c>
       <c r="AI2">
-        <v>0.7349078123630441</v>
+        <v>0.7476662336354132</v>
       </c>
       <c r="AJ2">
-        <v>0.5304975911215917</v>
+        <v>0.6741424475664309</v>
       </c>
       <c r="AK2">
-        <v>0.5083427905794337</v>
+        <v>0.6343031787302698</v>
       </c>
       <c r="AL2">
-        <v>9.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-329.62</v>
-      </c>
-      <c r="AO2">
-        <v>-0.3374233128834356</v>
-      </c>
-      <c r="AQ2">
-        <v>0.01001152842667314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0488</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="E3">
-        <v>0.116</v>
+        <v>0.0735</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3363.5</v>
+        <v>3127.6</v>
       </c>
       <c r="L3">
-        <v>0.3142253902710176</v>
+        <v>0.2898421789133235</v>
       </c>
       <c r="M3">
-        <v>2826.4</v>
+        <v>3210.1</v>
       </c>
       <c r="N3">
-        <v>0.1094998818374471</v>
+        <v>0.1769664160179938</v>
       </c>
       <c r="O3">
-        <v>0.8403151479114018</v>
+        <v>1.026378053459522</v>
       </c>
       <c r="P3">
-        <v>2826.4</v>
+        <v>3210.1</v>
       </c>
       <c r="Q3">
-        <v>0.1094998818374471</v>
+        <v>0.1769664160179938</v>
       </c>
       <c r="R3">
-        <v>0.8403151479114018</v>
+        <v>1.026378053459522</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>60538.2</v>
+        <v>39718.2</v>
       </c>
       <c r="V3">
-        <v>2.345360085851874</v>
+        <v>2.189585216873581</v>
       </c>
       <c r="W3">
-        <v>0.1309478388837412</v>
+        <v>0.119181172453739</v>
       </c>
       <c r="X3">
-        <v>0.135962191864459</v>
+        <v>0.1702099670074133</v>
       </c>
       <c r="Y3">
-        <v>-0.005014352980717812</v>
+        <v>-0.05102879455367436</v>
       </c>
       <c r="Z3">
-        <v>0.232954582550768</v>
+        <v>0.1262956460674158</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0576636278181325</v>
+        <v>0.06052728485804984</v>
       </c>
       <c r="AC3">
-        <v>-0.0576636278181325</v>
+        <v>-0.06052728485804984</v>
       </c>
       <c r="AD3">
-        <v>120695.4</v>
+        <v>124741.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>120695.4</v>
+        <v>124741.2</v>
       </c>
       <c r="AG3">
-        <v>60157.2</v>
+        <v>85023</v>
       </c>
       <c r="AH3">
-        <v>0.8238183353320961</v>
+        <v>0.8730438239427551</v>
       </c>
       <c r="AI3">
-        <v>0.788695929468162</v>
+        <v>0.7951873587207767</v>
       </c>
       <c r="AJ3">
-        <v>0.6997537487306484</v>
+        <v>0.8241649590064616</v>
       </c>
       <c r="AK3">
-        <v>0.6503945146356389</v>
+        <v>0.7257494537011745</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
+        <v>0.08410000000000001</v>
+      </c>
+      <c r="E4">
         <v>0.0433</v>
       </c>
-      <c r="E4">
-        <v>0.0755</v>
-      </c>
       <c r="F4">
-        <v>0.0696</v>
+        <v>0.0426</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,201 +856,91 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3574.3</v>
+        <v>3320.3</v>
       </c>
       <c r="L4">
-        <v>0.3610221705974446</v>
+        <v>0.2749844714066835</v>
       </c>
       <c r="M4">
-        <v>1980.3</v>
+        <v>3997.3</v>
       </c>
       <c r="N4">
-        <v>0.07379926659113947</v>
+        <v>0.1306947850253392</v>
       </c>
       <c r="O4">
-        <v>0.5540385530033853</v>
+        <v>1.203897238201367</v>
       </c>
       <c r="P4">
-        <v>1819.4</v>
+        <v>2286.4</v>
       </c>
       <c r="Q4">
-        <v>0.0678030528889154</v>
+        <v>0.07475559914991009</v>
       </c>
       <c r="R4">
-        <v>0.5090227457124472</v>
+        <v>0.6886124747763757</v>
       </c>
       <c r="S4">
-        <v>160.9000000000001</v>
+        <v>1710.9</v>
       </c>
       <c r="T4">
-        <v>0.08125031560874618</v>
+        <v>0.4280139093888375</v>
       </c>
       <c r="U4">
-        <v>46186.5</v>
+        <v>31677.4</v>
       </c>
       <c r="V4">
-        <v>1.721218919563532</v>
+        <v>1.035716854667321</v>
       </c>
       <c r="W4">
-        <v>0.1818898879949519</v>
+        <v>0.1314486149655771</v>
       </c>
       <c r="X4">
-        <v>0.09012358578028</v>
+        <v>0.08951708632155161</v>
       </c>
       <c r="Y4">
-        <v>0.09176630221467187</v>
+        <v>0.04193152864402544</v>
       </c>
       <c r="Z4">
-        <v>1.235662668646955</v>
+        <v>0.4240892679020496</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05961262096857506</v>
+        <v>0.06301040419986541</v>
       </c>
       <c r="AC4">
-        <v>-0.05961262096857506</v>
+        <v>-0.06301040419986541</v>
       </c>
       <c r="AD4">
-        <v>49398.8</v>
+        <v>47457.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>49398.8</v>
+        <v>47457.1</v>
       </c>
       <c r="AG4">
-        <v>3212.300000000003</v>
+        <v>15779.7</v>
       </c>
       <c r="AH4">
-        <v>0.6480026865217415</v>
+        <v>0.6080961429792381</v>
       </c>
       <c r="AI4">
-        <v>0.6616669858997215</v>
+        <v>0.6461653881450135</v>
       </c>
       <c r="AJ4">
-        <v>0.1069130896395183</v>
+        <v>0.3403386628189118</v>
       </c>
       <c r="AK4">
-        <v>0.1128247095351158</v>
+        <v>0.3778048593619813</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KBC Ancora SCA (ENXTBR:KBCA)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>0.068</v>
-      </c>
-      <c r="K5">
-        <v>326.3</v>
-      </c>
-      <c r="M5">
-        <v>328.2</v>
-      </c>
-      <c r="N5">
-        <v>0.09285875961973743</v>
-      </c>
-      <c r="O5">
-        <v>1.005822862396567</v>
-      </c>
-      <c r="P5">
-        <v>278.3</v>
-      </c>
-      <c r="Q5">
-        <v>0.07874038026256225</v>
-      </c>
-      <c r="R5">
-        <v>0.8528961078761875</v>
-      </c>
-      <c r="S5">
-        <v>49.89999999999998</v>
-      </c>
-      <c r="T5">
-        <v>0.152041438147471</v>
-      </c>
-      <c r="U5">
-        <v>0.215</v>
-      </c>
-      <c r="V5">
-        <v>6.083069262109551e-05</v>
-      </c>
-      <c r="W5">
-        <v>0.09083569957129337</v>
-      </c>
-      <c r="X5">
-        <v>0.06085776077857287</v>
-      </c>
-      <c r="Y5">
-        <v>0.0299779387927205</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>-0.0008760751831793565</v>
-      </c>
-      <c r="AB5">
-        <v>0.06019308409016239</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06106915927334174</v>
-      </c>
-      <c r="AD5">
-        <v>109.2</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>109.2</v>
-      </c>
-      <c r="AG5">
-        <v>108.985</v>
-      </c>
-      <c r="AH5">
-        <v>0.02997035898561862</v>
-      </c>
-      <c r="AI5">
-        <v>0.02793839226321445</v>
-      </c>
-      <c r="AJ5">
-        <v>0.02991311651115652</v>
-      </c>
-      <c r="AK5">
-        <v>0.02788491921855191</v>
-      </c>
-      <c r="AL5">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="AM5">
-        <v>-329.62</v>
-      </c>
-      <c r="AO5">
-        <v>-0.3374233128834356</v>
-      </c>
-      <c r="AQ5">
-        <v>0.01001152842667314</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -591,7 +591,7 @@
         <v>0.07050000000000001</v>
       </c>
       <c r="E2">
-        <v>0.05839999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="F2">
         <v>0.0426</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.0001495722757727901</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.000124070082078487</v>
       </c>
       <c r="K2">
-        <v>6447.9</v>
+        <v>6842.5</v>
       </c>
       <c r="L2">
-        <v>0.2819962213319804</v>
+        <v>0.2992538880044784</v>
       </c>
       <c r="M2">
-        <v>7207.4</v>
+        <v>7544.9</v>
       </c>
       <c r="N2">
-        <v>0.1479211732882363</v>
+        <v>0.1430285681788023</v>
       </c>
       <c r="O2">
-        <v>1.117790288310923</v>
+        <v>1.10265253927658</v>
       </c>
       <c r="P2">
-        <v>5496.5</v>
+        <v>5834</v>
       </c>
       <c r="Q2">
-        <v>0.1128074935453549</v>
+        <v>0.1105950598092927</v>
       </c>
       <c r="R2">
-        <v>0.8524480838722686</v>
+        <v>0.8526123492875411</v>
       </c>
       <c r="S2">
         <v>1710.9</v>
       </c>
       <c r="T2">
-        <v>0.2373810250575797</v>
+        <v>0.2267624488064786</v>
       </c>
       <c r="U2">
-        <v>71395.60000000001</v>
+        <v>71395.601</v>
       </c>
       <c r="V2">
-        <v>1.465288581127398</v>
+        <v>1.353445451271066</v>
       </c>
       <c r="W2">
-        <v>0.125314893709658</v>
+        <v>0.119181172453739</v>
       </c>
       <c r="X2">
-        <v>0.1298635266644825</v>
+        <v>0.08949667001123515</v>
       </c>
       <c r="Y2">
-        <v>-0.004548632954824466</v>
+        <v>0.02968450244250383</v>
       </c>
       <c r="Z2">
-        <v>0.200727581738822</v>
+        <v>0.1940689433969967</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06176884452895762</v>
+        <v>0.06300240296910625</v>
       </c>
       <c r="AC2">
-        <v>-0.06176884452895762</v>
+        <v>-0.06300240296910625</v>
       </c>
       <c r="AD2">
-        <v>172198.3</v>
+        <v>172322.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>172198.3</v>
+        <v>172322.2</v>
       </c>
       <c r="AG2">
-        <v>100802.7</v>
+        <v>100926.599</v>
       </c>
       <c r="AH2">
-        <v>0.7794497537376162</v>
+        <v>0.7656273603432128</v>
       </c>
       <c r="AI2">
-        <v>0.7476662336354132</v>
+        <v>0.7358822125208555</v>
       </c>
       <c r="AJ2">
-        <v>0.6741424475664309</v>
+        <v>0.6567424247694031</v>
       </c>
       <c r="AK2">
-        <v>0.6343031787302698</v>
+        <v>0.6200363299593754</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-398.03</v>
+      </c>
+      <c r="AO2">
+        <v>-0.4704264099037139</v>
+      </c>
+      <c r="AQ2">
+        <v>0.008592317162022963</v>
       </c>
     </row>
     <row r="3">
@@ -770,10 +776,10 @@
         <v>0.119181172453739</v>
       </c>
       <c r="X3">
-        <v>0.1702099670074133</v>
+        <v>0.17015186632627</v>
       </c>
       <c r="Y3">
-        <v>-0.05102879455367436</v>
+        <v>-0.05097069387253104</v>
       </c>
       <c r="Z3">
         <v>0.1262956460674158</v>
@@ -782,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06052728485804984</v>
+        <v>0.06051990861774556</v>
       </c>
       <c r="AC3">
-        <v>-0.06052728485804984</v>
+        <v>-0.06051990861774556</v>
       </c>
       <c r="AD3">
         <v>124741.2</v>
@@ -895,10 +901,10 @@
         <v>0.1314486149655771</v>
       </c>
       <c r="X4">
-        <v>0.08951708632155161</v>
+        <v>0.08949667001123515</v>
       </c>
       <c r="Y4">
-        <v>0.04193152864402544</v>
+        <v>0.0419519449543419</v>
       </c>
       <c r="Z4">
         <v>0.4240892679020496</v>
@@ -907,10 +913,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06301040419986541</v>
+        <v>0.06300240296910625</v>
       </c>
       <c r="AC4">
-        <v>-0.06301040419986541</v>
+        <v>-0.06300240296910625</v>
       </c>
       <c r="AD4">
         <v>47457.1</v>
@@ -941,6 +947,116 @@
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KBC Ancora SA (ENXTBR:KBCA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0.0774</v>
+      </c>
+      <c r="K5">
+        <v>394.6</v>
+      </c>
+      <c r="M5">
+        <v>337.5</v>
+      </c>
+      <c r="N5">
+        <v>0.08382177627657461</v>
+      </c>
+      <c r="O5">
+        <v>0.855296502787633</v>
+      </c>
+      <c r="P5">
+        <v>337.5</v>
+      </c>
+      <c r="Q5">
+        <v>0.08382177627657461</v>
+      </c>
+      <c r="R5">
+        <v>0.855296502787633</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.001</v>
+      </c>
+      <c r="V5">
+        <v>2.483608185972581E-07</v>
+      </c>
+      <c r="W5">
+        <v>0.1038585039743117</v>
+      </c>
+      <c r="X5">
+        <v>0.06646110179728849</v>
+      </c>
+      <c r="Y5">
+        <v>0.03739740217702324</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-0.0008750417371881225</v>
+      </c>
+      <c r="AB5">
+        <v>0.06576974083318517</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06664478257037329</v>
+      </c>
+      <c r="AD5">
+        <v>123.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>123.9</v>
+      </c>
+      <c r="AG5">
+        <v>123.899</v>
+      </c>
+      <c r="AH5">
+        <v>0.02985326361949739</v>
+      </c>
+      <c r="AI5">
+        <v>0.03212757681835861</v>
+      </c>
+      <c r="AJ5">
+        <v>0.02985302986604098</v>
+      </c>
+      <c r="AK5">
+        <v>0.03212732584657743</v>
+      </c>
+      <c r="AL5">
+        <v>7.27</v>
+      </c>
+      <c r="AM5">
+        <v>-398.03</v>
+      </c>
+      <c r="AO5">
+        <v>-0.4704264099037139</v>
+      </c>
+      <c r="AQ5">
+        <v>0.008592317162022963</v>
       </c>
     </row>
   </sheetData>
